--- a/config/辅控/消防温感烟感.xlsx
+++ b/config/辅控/消防温感烟感.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22010" windowHeight="12332"/>
+    <workbookView windowWidth="22010" windowHeight="12332" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="遥测" sheetId="1" r:id="rId1"/>
@@ -138,7 +138,7 @@
     <t>修改modbus地址</t>
   </si>
   <si>
-    <t>modifyModbusAddress</t>
+    <t>modifyModbusAddr</t>
   </si>
   <si>
     <t>{"en":"Modify Modbus address"}</t>
@@ -147,7 +147,7 @@
     <t>开电磁阀500ms</t>
   </si>
   <si>
-    <t>openTheSolenoidValveFor500ms</t>
+    <t>openSolenoidValveFor500ms</t>
   </si>
   <si>
     <t>{"en":"Open the solenoid valve for 500ms"}</t>
@@ -156,7 +156,7 @@
     <t>开电磁阀</t>
   </si>
   <si>
-    <t>openTheSolenoidValve</t>
+    <t>openSolenoidValve</t>
   </si>
   <si>
     <t>{"en":"Open the solenoid valve"}</t>
@@ -165,7 +165,7 @@
     <t>关电磁阀</t>
   </si>
   <si>
-    <t>closeTheSolenoidValve</t>
+    <t>closeSolenoidValve</t>
   </si>
   <si>
     <t>{"en":"Close the solenoid valve"}</t>
@@ -1486,7 +1486,7 @@
     <col min="3" max="6" width="9" style="2"/>
     <col min="7" max="7" width="16.7222222222222" style="2" customWidth="1"/>
     <col min="8" max="12" width="9" style="2"/>
-    <col min="13" max="13" width="21.9761904761905" style="2" customWidth="1"/>
+    <col min="13" max="13" width="27.6746031746032" style="2" customWidth="1"/>
     <col min="14" max="14" width="31.3412698412698" style="2" customWidth="1"/>
     <col min="15" max="16384" width="9" style="2"/>
   </cols>
